--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25277.69</v>
+        <v>26394.01</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>27035.37</v>
+        <v>28229.31</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2923.42</v>
+        <v>3052.53</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>34480.99</v>
+        <v>36003.74</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>75833.08</v>
+        <v>79182.00999999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13989.4</v>
+        <v>14607.2</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26722.26</v>
+        <v>27902.37</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>26574.31</v>
+        <v>27747.88</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>78305.89</v>
+        <v>80580.41</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1978.25</v>
+        <v>2035.71</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>325.75</v>
+        <v>335.21</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3869.07</v>
+        <v>3981.45</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8983.77</v>
+        <v>9244.719999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8305.65</v>
+        <v>8546.9</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>31322.36</v>
+        <v>32232.16</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2782.48</v>
+        <v>2863.3</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6645</v>
+        <v>6838.01</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1895.83</v>
+        <v>1950.89</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1769.44</v>
+        <v>1820.83</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1648.54</v>
+        <v>1696.43</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>19.34</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>610.79</v>
+        <v>613.1900000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10300.1</v>
+        <v>10340.71</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1071.22</v>
+        <v>1075.45</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>5813.21</v>
+        <v>5836.13</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2198.06</v>
+        <v>2206.73</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>212.99</v>
+        <v>213.83</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1242.45</v>
+        <v>1247.35</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2756.37</v>
+        <v>2767.23</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5231.04</v>
+        <v>5251.67</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>13188.4</v>
+        <v>13240.39</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1648.54</v>
+        <v>1655.04</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6594.18</v>
+        <v>6620.18</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>29176.78</v>
+        <v>29291.81</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4396.12</v>
+        <v>4413.45</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>161622.89</v>
+        <v>164286.67</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10430.07</v>
+        <v>10601.97</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>18271.37</v>
+        <v>18572.51</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>34436.76</v>
+        <v>35004.33</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>483.57</v>
+        <v>491.54</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>22766.45</v>
+        <v>23141.67</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>20484.82</v>
+        <v>20822.44</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>29739.75</v>
+        <v>30229.91</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3297.09</v>
+        <v>3351.43</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5418.25</v>
+        <v>5507.55</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1099.03</v>
+        <v>1117.14</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>19800.95</v>
+        <v>19849.67</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>51612.98</v>
+        <v>51739.97</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>13408.17</v>
+        <v>13441.16</v>
       </c>
     </row>
     <row r="51">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>163145.07</v>
+        <v>163546.47</v>
       </c>
     </row>
     <row r="52">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7693.21</v>
+        <v>7712.14</v>
       </c>
     </row>
     <row r="53">
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>14572</v>
+        <v>14607.85</v>
       </c>
     </row>
     <row r="54">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3890.57</v>
+        <v>3900.14</v>
       </c>
     </row>
     <row r="55">
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>32728.39</v>
+        <v>32808.91</v>
       </c>
     </row>
     <row r="56">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1740.86</v>
+        <v>1745.15</v>
       </c>
     </row>
     <row r="57">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>13165.83</v>
+        <v>13198.22</v>
       </c>
     </row>
     <row r="58">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3296.16</v>
+        <v>3304.27</v>
       </c>
     </row>
     <row r="59">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>68942.75</v>
+        <v>69112.38</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>12424.54</v>
+        <v>12455.1</v>
       </c>
     </row>
     <row r="61">
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6963.45</v>
+        <v>6980.59</v>
       </c>
     </row>
     <row r="62">
@@ -4233,7 +4233,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>445.11</v>
+        <v>446.2</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>68764.11</v>
+        <v>68933.3</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4052.07</v>
+        <v>3999.9</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4767.26</v>
+        <v>4705.89</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>41286.42</v>
+        <v>40754.89</v>
       </c>
     </row>
     <row r="67">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>439.61</v>
+        <v>433.95</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>12089.33</v>
+        <v>11933.69</v>
       </c>
     </row>
     <row r="69">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2901.44</v>
+        <v>2864.09</v>
       </c>
     </row>
     <row r="70">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3903.89</v>
+        <v>3853.63</v>
       </c>
     </row>
     <row r="71">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5692.26</v>
+        <v>5618.98</v>
       </c>
     </row>
     <row r="72">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>13955.92</v>
+        <v>13776.25</v>
       </c>
     </row>
     <row r="73">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>240876.54</v>
+        <v>237775.48</v>
       </c>
     </row>
     <row r="74">
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2198.06</v>
+        <v>2169.76</v>
       </c>
     </row>
     <row r="75">
@@ -5034,7 +5034,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>164854.51</v>
+        <v>162732.16</v>
       </c>
     </row>
     <row r="76">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>189.03</v>
+        <v>186.6</v>
       </c>
     </row>
     <row r="77">
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1951.38</v>
+        <v>1926.26</v>
       </c>
     </row>
     <row r="78">
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>16757.46</v>
+        <v>16639.2</v>
       </c>
     </row>
     <row r="79">
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>60446.66</v>
+        <v>60020.08</v>
       </c>
     </row>
     <row r="80">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>25711.69</v>
+        <v>25530.24</v>
       </c>
     </row>
     <row r="81">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2084.82</v>
+        <v>2070.1</v>
       </c>
     </row>
     <row r="82">
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>12391.12</v>
+        <v>12303.68</v>
       </c>
     </row>
     <row r="83">
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>16063.57</v>
+        <v>15950.2</v>
       </c>
     </row>
     <row r="84">
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1867.64</v>
+        <v>1854.46</v>
       </c>
     </row>
     <row r="85">
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>11500.15</v>
+        <v>11418.99</v>
       </c>
     </row>
     <row r="86">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>21470.95</v>
+        <v>21319.43</v>
       </c>
     </row>
     <row r="87">
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>21925.65</v>
+        <v>21770.92</v>
       </c>
     </row>
     <row r="88">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>20329.67</v>
+        <v>20186.21</v>
       </c>
     </row>
     <row r="89">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>8723.280000000001</v>
+        <v>8661.719999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11526.63</v>
+        <v>11445.28</v>
       </c>
     </row>
     <row r="91">
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>45514.52</v>
+        <v>45193.32</v>
       </c>
     </row>
     <row r="92">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>27346.51</v>
+        <v>27153.52</v>
       </c>
     </row>
     <row r="93">
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>29144.41</v>
+        <v>28938.74</v>
       </c>
     </row>
     <row r="94">
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2307.86</v>
+        <v>2291.57</v>
       </c>
     </row>
     <row r="95">
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>339.85</v>
+        <v>337.45</v>
       </c>
     </row>
     <row r="96">
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>24822.66</v>
+        <v>25272.71</v>
       </c>
     </row>
     <row r="97">
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>13888.44</v>
+        <v>14140.25</v>
       </c>
     </row>
     <row r="98">
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>24849.07</v>
+        <v>25299.6</v>
       </c>
     </row>
     <row r="99">
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>7131.68</v>
+        <v>7260.99</v>
       </c>
     </row>
     <row r="100">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2198.06</v>
+        <v>2237.91</v>
       </c>
     </row>
     <row r="101">
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2198.06</v>
+        <v>2237.91</v>
       </c>
     </row>
     <row r="102">
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>11162.24</v>
+        <v>11364.62</v>
       </c>
     </row>
     <row r="103">
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>12688.63</v>
+        <v>12887.39</v>
       </c>
     </row>
     <row r="104">
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>298.58</v>
+        <v>303.26</v>
       </c>
     </row>
     <row r="105">
@@ -6864,7 +6864,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>22157.44</v>
+        <v>22504.52</v>
       </c>
     </row>
     <row r="106">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>14095.06</v>
+        <v>14315.85</v>
       </c>
     </row>
     <row r="107">
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2198.06</v>
+        <v>2232.49</v>
       </c>
     </row>
     <row r="108">
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>154.96</v>
+        <v>157.39</v>
       </c>
     </row>
     <row r="109">
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2503.33</v>
+        <v>2542.55</v>
       </c>
     </row>
     <row r="110">
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3857.82</v>
+        <v>3918.25</v>
       </c>
     </row>
     <row r="111">
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1381.32</v>
+        <v>1402.95</v>
       </c>
     </row>
     <row r="112">
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>351.69</v>
+        <v>357.2</v>
       </c>
     </row>
     <row r="113">
@@ -7352,7 +7352,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>395.65</v>
+        <v>401.85</v>
       </c>
     </row>
     <row r="114">
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>167.73</v>
+        <v>170.36</v>
       </c>
     </row>
     <row r="115">
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>595.13</v>
+        <v>604.45</v>
       </c>
     </row>
     <row r="116">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>413.45</v>
+        <v>419.93</v>
       </c>
     </row>
     <row r="117">
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1705.69</v>
+        <v>1705.61</v>
       </c>
     </row>
     <row r="118">
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1050.76</v>
+        <v>1050.71</v>
       </c>
     </row>
     <row r="119">
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>11827.32</v>
+        <v>11826.71</v>
       </c>
     </row>
     <row r="120">
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4969.81</v>
+        <v>4969.56</v>
       </c>
     </row>
     <row r="121">
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>85952.24000000001</v>
+        <v>85947.82000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7901,7 +7901,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>9559.58</v>
+        <v>9559.09</v>
       </c>
     </row>
     <row r="123">
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>26376.72</v>
+        <v>26375.36</v>
       </c>
     </row>
     <row r="124">
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>12811.1</v>
+        <v>12810.44</v>
       </c>
     </row>
     <row r="125">
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>207795.82</v>
+        <v>207785.13</v>
       </c>
     </row>
     <row r="126">
@@ -8149,7 +8149,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>34046.88</v>
+        <v>34045.13</v>
       </c>
     </row>
     <row r="127">
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>7392.08</v>
+        <v>7391.7</v>
       </c>
     </row>
     <row r="128">
@@ -8271,7 +8271,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2304.87</v>
+        <v>2304.75</v>
       </c>
     </row>
     <row r="129">
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1383.93</v>
+        <v>1383.86</v>
       </c>
     </row>
     <row r="130">
@@ -8393,7 +8393,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2039.43</v>
+        <v>2030.31</v>
       </c>
     </row>
     <row r="131">
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>544.5700000000001</v>
+        <v>542.14</v>
       </c>
     </row>
     <row r="132">
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>338.28</v>
+        <v>336.77</v>
       </c>
     </row>
     <row r="133">
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>26494.54</v>
+        <v>26376.07</v>
       </c>
     </row>
     <row r="134">
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1133.12</v>
+        <v>1128.05</v>
       </c>
     </row>
     <row r="135">
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>9973.040000000001</v>
+        <v>9928.450000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8759,7 +8759,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>40774.4</v>
+        <v>40592.08</v>
       </c>
     </row>
     <row r="137">
@@ -8820,7 +8820,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>8240.389999999999</v>
+        <v>8203.540000000001</v>
       </c>
     </row>
     <row r="138">
@@ -8881,7 +8881,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>867.11</v>
+        <v>863.23</v>
       </c>
     </row>
     <row r="139">
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2429.05</v>
+        <v>2418.19</v>
       </c>
     </row>
     <row r="140">
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>5495.15</v>
+        <v>5499.88</v>
       </c>
     </row>
     <row r="141">
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>8200.190000000001</v>
+        <v>8207.26</v>
       </c>
     </row>
     <row r="142">
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3604.85</v>
+        <v>3607.95</v>
       </c>
     </row>
     <row r="143">
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4332.82</v>
+        <v>4336.55</v>
       </c>
     </row>
     <row r="144">
@@ -9247,7 +9247,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2742.08</v>
+        <v>2744.44</v>
       </c>
     </row>
     <row r="145">
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>17958.15</v>
+        <v>17973.62</v>
       </c>
     </row>
     <row r="146">
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>23695.09</v>
+        <v>23715.5</v>
       </c>
     </row>
     <row r="147">
@@ -9430,7 +9430,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>725.36</v>
+        <v>725.98</v>
       </c>
     </row>
     <row r="148">
@@ -9491,7 +9491,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>27010.31</v>
+        <v>27033.58</v>
       </c>
     </row>
     <row r="149">
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>14869.88</v>
+        <v>14882.69</v>
       </c>
     </row>
     <row r="150">
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>45328.15</v>
+        <v>45367.2</v>
       </c>
     </row>
     <row r="151">
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>33907.77</v>
+        <v>33936.98</v>
       </c>
     </row>
     <row r="152">
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>544.02</v>
+        <v>544.49</v>
       </c>
     </row>
     <row r="153">
@@ -9796,7 +9796,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>17988.92</v>
+        <v>18063.23</v>
       </c>
     </row>
     <row r="154">
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>261.13</v>
+        <v>262.21</v>
       </c>
     </row>
     <row r="155">
@@ -9918,7 +9918,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>9198.33</v>
+        <v>9236.33</v>
       </c>
     </row>
     <row r="156">
@@ -9979,7 +9979,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>22107.95</v>
+        <v>22199.27</v>
       </c>
     </row>
     <row r="157">
@@ -10040,7 +10040,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>8861.290000000001</v>
+        <v>8897.9</v>
       </c>
     </row>
     <row r="158">
@@ -10101,7 +10101,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>5530.48</v>
+        <v>5553.33</v>
       </c>
     </row>
     <row r="159">
@@ -10162,7 +10162,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>21014.17</v>
+        <v>21100.98</v>
       </c>
     </row>
     <row r="160">
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1648.54</v>
+        <v>1655.35</v>
       </c>
     </row>
     <row r="161">
@@ -10284,7 +10284,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1257.29</v>
+        <v>1262.48</v>
       </c>
     </row>
     <row r="162">
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>1362.8</v>
+        <v>1368.43</v>
       </c>
     </row>
     <row r="163">
@@ -10406,7 +10406,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>3425.68</v>
+        <v>3416.23</v>
       </c>
     </row>
     <row r="164">
@@ -10467,7 +10467,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>6397.23</v>
+        <v>6379.58</v>
       </c>
     </row>
     <row r="165">
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1098.18</v>
+        <v>1095.15</v>
       </c>
     </row>
     <row r="166">
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>251.46</v>
+        <v>250.76</v>
       </c>
     </row>
     <row r="167">
@@ -10650,7 +10650,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2901.44</v>
+        <v>2893.44</v>
       </c>
     </row>
     <row r="168">
@@ -10711,7 +10711,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1677.31</v>
+        <v>1672.69</v>
       </c>
     </row>
     <row r="169">
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>725.36</v>
+        <v>723.36</v>
       </c>
     </row>
     <row r="170">
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1216.46</v>
+        <v>1202.42</v>
       </c>
     </row>
     <row r="171">
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>11437.82</v>
+        <v>11305.78</v>
       </c>
     </row>
     <row r="172">
@@ -10955,7 +10955,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1556.74</v>
+        <v>1538.77</v>
       </c>
     </row>
     <row r="173">
@@ -11016,7 +11016,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>36662.78</v>
+        <v>36239.53</v>
       </c>
     </row>
     <row r="174">
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>254336.28</v>
+        <v>251400.14</v>
       </c>
     </row>
     <row r="175">
@@ -11142,7 +11142,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>643.15</v>
+        <v>635.73</v>
       </c>
     </row>
     <row r="176">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>120893.31</v>
+        <v>119497.68</v>
       </c>
     </row>
     <row r="177">
@@ -11268,7 +11268,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1318.84</v>
+        <v>1303.61</v>
       </c>
     </row>
     <row r="178">
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>16485.45</v>
+        <v>16295.14</v>
       </c>
     </row>
     <row r="179">
@@ -11390,7 +11390,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2010.7</v>
+        <v>1987.49</v>
       </c>
     </row>
     <row r="180">
@@ -11451,7 +11451,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2190.24</v>
+        <v>2164.96</v>
       </c>
     </row>
     <row r="181">
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1373.79</v>
+        <v>1357.93</v>
       </c>
     </row>
     <row r="182">
@@ -11573,7 +11573,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>28095.61</v>
+        <v>27771.26</v>
       </c>
     </row>
     <row r="183">
@@ -11634,7 +11634,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>10599.93</v>
+        <v>10441.82</v>
       </c>
     </row>
     <row r="184">
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3889.75</v>
+        <v>3831.74</v>
       </c>
     </row>
     <row r="185">
@@ -11756,7 +11756,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>36083.47</v>
+        <v>35545.27</v>
       </c>
     </row>
     <row r="186">
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>10670.48</v>
+        <v>10511.33</v>
       </c>
     </row>
     <row r="187">
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>729.76</v>
+        <v>718.87</v>
       </c>
     </row>
     <row r="188">
@@ -11939,7 +11939,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>12158.71</v>
+        <v>11977.36</v>
       </c>
     </row>
     <row r="189">
@@ -12004,7 +12004,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>325312.26</v>
+        <v>320460.14</v>
       </c>
     </row>
     <row r="190">
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>29485.41</v>
+        <v>29045.62</v>
       </c>
     </row>
     <row r="191">
@@ -12126,7 +12126,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1648.55</v>
+        <v>1623.96</v>
       </c>
     </row>
     <row r="192">
@@ -12187,7 +12187,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>55866.78</v>
+        <v>55033.51</v>
       </c>
     </row>
     <row r="193">
@@ -12248,7 +12248,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1868.35</v>
+        <v>1840.48</v>
       </c>
     </row>
     <row r="194">
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3508.1</v>
+        <v>3455.78</v>
       </c>
     </row>
     <row r="195">
@@ -12370,7 +12370,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1160.58</v>
+        <v>1153.91</v>
       </c>
     </row>
     <row r="196">
@@ -12431,7 +12431,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>34993.34</v>
+        <v>34792.33</v>
       </c>
     </row>
     <row r="197">
@@ -12492,7 +12492,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>6460.76</v>
+        <v>6423.65</v>
       </c>
     </row>
     <row r="198">
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>15752.68</v>
+        <v>15662.19</v>
       </c>
     </row>
     <row r="199">
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>17584.48</v>
+        <v>17483.47</v>
       </c>
     </row>
     <row r="200">
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>3094.87</v>
+        <v>3077.09</v>
       </c>
     </row>
     <row r="201">
@@ -12736,7 +12736,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>16132</v>
+        <v>16039.34</v>
       </c>
     </row>
     <row r="202">
@@ -12801,7 +12801,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>79462.17</v>
+        <v>79005.72</v>
       </c>
     </row>
     <row r="203">
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>4208.52</v>
+        <v>4184.34</v>
       </c>
     </row>
     <row r="204">
@@ -12923,7 +12923,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>51251.03</v>
+        <v>50956.63</v>
       </c>
     </row>
     <row r="205">
@@ -12984,7 +12984,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>14419.25</v>
+        <v>14336.42</v>
       </c>
     </row>
     <row r="206">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>10761.18</v>
+        <v>10692.24</v>
       </c>
     </row>
     <row r="207">
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>46159.38</v>
+        <v>45863.66</v>
       </c>
     </row>
     <row r="208">
@@ -13167,7 +13167,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>16087.16</v>
+        <v>15984.1</v>
       </c>
     </row>
     <row r="209">
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>50954.69</v>
+        <v>50628.25</v>
       </c>
     </row>
     <row r="210">
@@ -13289,7 +13289,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3622.23</v>
+        <v>3599.02</v>
       </c>
     </row>
     <row r="211">
@@ -13350,7 +13350,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>12089.33</v>
+        <v>12011.88</v>
       </c>
     </row>
     <row r="212">
@@ -13411,7 +13411,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>879.22</v>
+        <v>873.59</v>
       </c>
     </row>
     <row r="213">
@@ -13472,7 +13472,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1645.25</v>
+        <v>1634.71</v>
       </c>
     </row>
     <row r="214">
@@ -13533,7 +13533,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>4396.12</v>
+        <v>4367.96</v>
       </c>
     </row>
     <row r="215">
@@ -13594,7 +13594,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>6261.97</v>
+        <v>6221.85</v>
       </c>
     </row>
     <row r="216">
@@ -13655,7 +13655,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2527.77</v>
+        <v>2511.58</v>
       </c>
     </row>
     <row r="217">
@@ -13716,7 +13716,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>5880.25</v>
+        <v>5842.58</v>
       </c>
     </row>
     <row r="218">
@@ -13777,7 +13777,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>7693.21</v>
+        <v>7643.92</v>
       </c>
     </row>
     <row r="219">
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1328.07</v>
+        <v>1322.35</v>
       </c>
     </row>
     <row r="220">
@@ -13899,7 +13899,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>58248.59</v>
+        <v>57997.66</v>
       </c>
     </row>
     <row r="221">
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>7480.27</v>
+        <v>7448.05</v>
       </c>
     </row>
     <row r="222">
@@ -14021,7 +14021,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1373.79</v>
+        <v>1367.87</v>
       </c>
     </row>
     <row r="223">
@@ -14082,7 +14082,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>369.6</v>
+        <v>368.01</v>
       </c>
     </row>
     <row r="224">
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>12263.75</v>
+        <v>12210.91</v>
       </c>
     </row>
     <row r="225">
@@ -14204,7 +14204,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>989.13</v>
+        <v>984.87</v>
       </c>
     </row>
     <row r="226">
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>6600.66</v>
+        <v>6572.23</v>
       </c>
     </row>
     <row r="227">
@@ -14326,7 +14326,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>38466.05</v>
+        <v>38300.34</v>
       </c>
     </row>
     <row r="228">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>33.41</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="229">
@@ -14448,7 +14448,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>659.42</v>
+        <v>656.58</v>
       </c>
     </row>
     <row r="230">
@@ -14509,7 +14509,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>25.06</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="231">
@@ -14570,7 +14570,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>42906.41</v>
+        <v>42721.57</v>
       </c>
     </row>
     <row r="232">
@@ -14631,7 +14631,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>37421.86</v>
+        <v>37260.65</v>
       </c>
     </row>
     <row r="233">
@@ -14692,7 +14692,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>15452.89</v>
+        <v>15386.32</v>
       </c>
     </row>
     <row r="234">
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>30278.28</v>
+        <v>30147.84</v>
       </c>
     </row>
     <row r="235">
@@ -14814,7 +14814,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>164.85</v>
+        <v>164.14</v>
       </c>
     </row>
     <row r="236">
@@ -14875,7 +14875,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>13188.36</v>
+        <v>13131.55</v>
       </c>
     </row>
     <row r="237">
@@ -14936,7 +14936,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>338.5</v>
+        <v>337.04</v>
       </c>
     </row>
     <row r="238">
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>10995.71</v>
+        <v>10948.34</v>
       </c>
     </row>
     <row r="239">
@@ -15058,7 +15058,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>50.12</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="240">
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1044.52</v>
+        <v>1029.41</v>
       </c>
     </row>
     <row r="241">
@@ -15180,7 +15180,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>50179.94</v>
+        <v>49453.98</v>
       </c>
     </row>
     <row r="242">
@@ -15241,7 +15241,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>36372.19</v>
+        <v>35845.99</v>
       </c>
     </row>
     <row r="243">
@@ -15302,7 +15302,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>14837.97</v>
+        <v>14623.31</v>
       </c>
     </row>
     <row r="244">
@@ -15363,7 +15363,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>18796.29</v>
+        <v>18524.36</v>
       </c>
     </row>
     <row r="245">
@@ -15424,7 +15424,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>8541.610000000001</v>
+        <v>8418.030000000001</v>
       </c>
     </row>
     <row r="246">
@@ -15485,7 +15485,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>4251.49</v>
+        <v>4189.98</v>
       </c>
     </row>
     <row r="247">
@@ -15546,7 +15546,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>18015.58</v>
+        <v>17754.94</v>
       </c>
     </row>
     <row r="248">
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>8242.73</v>
+        <v>8123.48</v>
       </c>
     </row>
     <row r="249">
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>23079.82</v>
+        <v>22745.92</v>
       </c>
     </row>
     <row r="250">
@@ -15729,7 +15729,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1002.32</v>
+        <v>987.8200000000001</v>
       </c>
     </row>
     <row r="251">
@@ -15790,7 +15790,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>988.99</v>
+        <v>974.6900000000001</v>
       </c>
     </row>
     <row r="252">
@@ -15851,7 +15851,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2198.06</v>
+        <v>2166.26</v>
       </c>
     </row>
     <row r="253">
@@ -15912,7 +15912,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>39565.08</v>
+        <v>38992.69</v>
       </c>
     </row>
     <row r="254">
@@ -15973,7 +15973,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>9957.379999999999</v>
+        <v>9813.32</v>
       </c>
     </row>
     <row r="255">
@@ -16034,7 +16034,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>32970.9</v>
+        <v>32493.91</v>
       </c>
     </row>
     <row r="256">
@@ -16095,7 +16095,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>449.48</v>
+        <v>439.81</v>
       </c>
     </row>
     <row r="257">
@@ -16156,7 +16156,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>3587.95</v>
+        <v>3510.75</v>
       </c>
     </row>
     <row r="258">
@@ -16217,7 +16217,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>336.3</v>
+        <v>329.07</v>
       </c>
     </row>
     <row r="259">
@@ -16278,7 +16278,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>18793.41</v>
+        <v>18389.07</v>
       </c>
     </row>
     <row r="260">
@@ -16339,7 +16339,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>5283.22</v>
+        <v>5169.55</v>
       </c>
     </row>
     <row r="261">
@@ -16400,7 +16400,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>483.57</v>
+        <v>473.17</v>
       </c>
     </row>
     <row r="262">
@@ -16461,7 +16461,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>375.87</v>
+        <v>367.78</v>
       </c>
     </row>
     <row r="263">
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>55519.05</v>
+        <v>54324.56</v>
       </c>
     </row>
     <row r="264">
@@ -16583,7 +16583,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>12528.94</v>
+        <v>12259.38</v>
       </c>
     </row>
     <row r="265">
@@ -16644,7 +16644,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>885.38</v>
+        <v>866.33</v>
       </c>
     </row>
     <row r="266">
@@ -16705,7 +16705,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>28194.61</v>
+        <v>27588.01</v>
       </c>
     </row>
     <row r="267">
@@ -16766,7 +16766,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>5088.32</v>
+        <v>4978.84</v>
       </c>
     </row>
     <row r="268">
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>10250.24</v>
+        <v>10029.71</v>
       </c>
     </row>
     <row r="269">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>4665.47</v>
+        <v>4565.09</v>
       </c>
     </row>
     <row r="270">
@@ -16949,7 +16949,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>365.43</v>
+        <v>357.57</v>
       </c>
     </row>
     <row r="271">
@@ -17010,7 +17010,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>3654.27</v>
+        <v>3575.65</v>
       </c>
     </row>
     <row r="272">
@@ -17071,7 +17071,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>15877.83</v>
+        <v>15536.21</v>
       </c>
     </row>
     <row r="273">
@@ -17132,7 +17132,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>38094.36</v>
+        <v>37274.76</v>
       </c>
     </row>
     <row r="274">
@@ -17193,7 +17193,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>12732.24</v>
+        <v>12458.3</v>
       </c>
     </row>
     <row r="275">
@@ -17254,7 +17254,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>29074.25</v>
+        <v>28448.72</v>
       </c>
     </row>
     <row r="276">
@@ -17315,7 +17315,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>6264.47</v>
+        <v>6129.69</v>
       </c>
     </row>
     <row r="277">
@@ -17380,7 +17380,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>364084.82</v>
+        <v>356251.53</v>
       </c>
     </row>
     <row r="278">
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>771.9400000000001</v>
+        <v>755.33</v>
       </c>
     </row>
     <row r="279">
@@ -17502,7 +17502,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>2088.16</v>
+        <v>2039.57</v>
       </c>
     </row>
     <row r="280">
@@ -17563,7 +17563,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1099.03</v>
+        <v>1073.46</v>
       </c>
     </row>
     <row r="281">
@@ -17624,7 +17624,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>31061.34</v>
+        <v>30338.57</v>
       </c>
     </row>
     <row r="282">
@@ -17685,7 +17685,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>28685.01</v>
+        <v>28017.54</v>
       </c>
     </row>
     <row r="283">
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2740.83</v>
+        <v>2677.06</v>
       </c>
     </row>
     <row r="284">
@@ -17807,7 +17807,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>640.87</v>
+        <v>625.96</v>
       </c>
     </row>
     <row r="285">
@@ -17868,7 +17868,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>17232.79</v>
+        <v>16831.8</v>
       </c>
     </row>
     <row r="286">
@@ -17929,7 +17929,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>8243.68</v>
+        <v>8051.86</v>
       </c>
     </row>
     <row r="287">
@@ -17990,7 +17990,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>28459.91</v>
+        <v>27797.68</v>
       </c>
     </row>
     <row r="288">
@@ -18051,7 +18051,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>41495.86</v>
+        <v>40530.29</v>
       </c>
     </row>
     <row r="289">
@@ -18112,7 +18112,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>3512.47</v>
+        <v>3430.73</v>
       </c>
     </row>
     <row r="290">
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>30988.46</v>
+        <v>30267.39</v>
       </c>
     </row>
     <row r="291">
@@ -18234,7 +18234,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1121.01</v>
+        <v>1094.93</v>
       </c>
     </row>
     <row r="292">
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>4403.87</v>
+        <v>4301.39</v>
       </c>
     </row>
     <row r="293">
@@ -18356,7 +18356,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>2414.34</v>
+        <v>2358.16</v>
       </c>
     </row>
     <row r="294">
@@ -18417,7 +18417,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>10067.98</v>
+        <v>9833.700000000001</v>
       </c>
     </row>
     <row r="295">
@@ -18478,7 +18478,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>3290.41</v>
+        <v>3213.85</v>
       </c>
     </row>
     <row r="296">
@@ -18539,7 +18539,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1648.55</v>
+        <v>1610.19</v>
       </c>
     </row>
     <row r="297">
@@ -18600,7 +18600,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>5495.15</v>
+        <v>5367.28</v>
       </c>
     </row>
     <row r="298">
@@ -18661,7 +18661,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2747.58</v>
+        <v>2683.64</v>
       </c>
     </row>
     <row r="299">
@@ -18722,7 +18722,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>5534.66</v>
+        <v>5405.87</v>
       </c>
     </row>
     <row r="300">
@@ -18783,7 +18783,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2198.06</v>
+        <v>2146.91</v>
       </c>
     </row>
     <row r="301">
@@ -18848,7 +18848,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>120069.04</v>
+        <v>117275.14</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15282,7 +15282,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -17482,7 +17482,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18092,7 +18092,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18580,7 +18580,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Salud</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Social</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE ÑUBLE SERPAT</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8612,7 +8612,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Agencia de Promocion de la inversion extranjera</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE TARAPACÁ</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hospital de Queilen</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Jefatura Adm y log Campo Militar Valdivia</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Depto. Provincial Educación Llanquihue</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12837,7 +12837,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13142,7 +13142,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13813,7 +13813,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUIRIHUE</t>
+          <t>Ilustre Municipalidad de Quirihue</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14362,7 +14362,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14484,7 +14484,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14789,7 +14789,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Consultorio General Urbano Victor Domingo Silva</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Comité de Seguro Agricola</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17290,7 +17290,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18270,7 +18270,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Dirección Servicio Metropolitano Oriente</t>
+          <t>DIRECCION SERVICIO SALUD METROPOLITANO O</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>EMDN-RMA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/mar-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4352,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4413,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4474,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4535,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4596,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4657,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4718,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4779,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4840,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4966,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5027,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5088,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5149,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5210,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5271,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5332,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5393,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5454,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5515,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5576,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5637,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5698,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5759,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5820,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5881,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5942,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6003,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6064,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6125,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6186,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6247,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6308,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6369,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6430,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6491,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6552,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6613,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6674,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6735,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6796,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6857,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6918,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6979,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7040,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7101,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7162,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7223,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7284,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7345,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7406,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7467,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7528,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7589,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7650,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7711,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7772,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7833,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7894,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7955,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8016,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8142,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8203,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8264,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8325,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8386,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8447,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8508,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8569,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8630,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8691,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8752,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8813,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8874,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8935,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8996,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9057,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9118,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9179,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9240,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9301,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9362,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9423,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9484,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9545,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9606,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9667,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9728,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9789,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9850,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9911,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9972,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10033,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10094,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10155,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10216,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10277,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10338,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10399,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10460,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10521,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10582,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10643,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10704,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10765,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10826,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10887,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10948,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11009,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11135,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11261,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11322,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11383,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11444,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11505,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11566,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11627,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11688,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11749,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11810,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11871,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11932,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12058,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12119,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12180,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12241,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12302,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12363,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12424,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12485,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12546,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12607,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12668,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12729,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12855,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12916,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12977,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13038,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13099,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13160,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13221,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13282,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13343,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13404,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13465,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13526,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13587,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13648,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13709,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13770,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13831,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13892,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13953,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14014,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14075,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14136,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14197,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14258,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14319,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14380,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14441,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14502,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14563,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14624,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14685,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14746,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14807,7 +15707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14868,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14929,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14990,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15051,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15112,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15173,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15234,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15295,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15356,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15417,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15478,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15539,7 +16487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15600,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15661,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15722,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15783,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15844,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15905,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15966,7 +16942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16027,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16088,7 +17072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16149,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16210,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16271,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16332,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16393,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16454,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16515,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16576,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16637,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16698,7 +17722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16759,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16820,7 +17852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16881,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16942,7 +17982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17003,7 +18047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17064,7 +18112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17125,7 +18177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17186,7 +18242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17247,7 +18307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17308,7 +18372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17434,7 +18502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17495,7 +18567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17556,7 +18632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17617,7 +18697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17678,7 +18762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17739,7 +18827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17800,7 +18892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17861,7 +18957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17922,7 +19022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17983,7 +19087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18044,7 +19152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18105,7 +19217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18166,7 +19282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18227,7 +19347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18288,7 +19412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18349,7 +19477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18410,7 +19542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18471,7 +19607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18532,7 +19672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18593,7 +19737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18654,7 +19802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18715,7 +19867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18776,7 +19932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
